--- a/artfynd/A 22979-2021 artfynd.xlsx
+++ b/artfynd/A 22979-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126560013</v>
       </c>
       <c r="B2" t="n">
-        <v>80637</v>
+        <v>80668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22979-2021 artfynd.xlsx
+++ b/artfynd/A 22979-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126560013</v>
       </c>
       <c r="B2" t="n">
-        <v>80668</v>
+        <v>80671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Britta Lidberg, Jonas Örnborg</t>
+          <t>Jonas Örnborg, Britta Lidberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 22979-2021 artfynd.xlsx
+++ b/artfynd/A 22979-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126560013</v>
       </c>
       <c r="B2" t="n">
-        <v>80671</v>
+        <v>80668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonas Örnborg, Britta Lidberg</t>
+          <t>Britta Lidberg, Jonas Örnborg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
